--- a/survey-learning/template-export-forms-learning.xlsx
+++ b/survey-learning/template-export-forms-learning.xlsx
@@ -526,37 +526,37 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>L2-Q1: **D2 — Copilot Adoption** (modos Ask/Edit/Agent/Coding Agent, features, ganho mensurado): qual seu nível?</t>
+          <t>L2-Q1: **DS-D2 Copilot Adoption** (modos Ask/Edit/Agent/Coding Agent, features, ganho mensurado): qual seu nível?</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>L2-Q2: **D3 — Microsoft/GitHub Tooling** (Foundry, Spaces, Coding Agent, MCP, Spec Kit, GHAS): qual seu nível?</t>
+          <t>L2-Q2: **DS-D3 Microsoft/GitHub Tooling** (Foundry, Spaces, Coding Agent, MCP, Spec Kit, GHAS): qual seu nível?</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>L2-Q3: **D4 — AI Dev Practices** (TDD com IA, SDD, pair programming, debugging com IA): qual seu nível?</t>
+          <t>L2-Q3: **DS-D4 AI Dev Practices** (TDD com IA, SDD, pair programming, debugging com IA): qual seu nível?</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">L2-Q4: **D5 — Agent Concepts** (custom agents, skills, prompts, MCP, A2A, handoffs, subagentes, personas Agentic DevOps): qual </t>
+          <t xml:space="preserve">L2-Q4: **DS-D5 Agent Concepts** (custom agents, skills, prompts, MCP, A2A, handoffs, subagentes, personas Agentic DevOps): qual </t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>L2-Q5: **D6 — Instructions / Memory** (copilot-instructions.md, AGENTS.md, CLAUDE.md, Spaces, prompt library): qual seu nível?</t>
+          <t>L2-Q5: **DS-D6 Instructions / Memory** (copilot-instructions.md, AGENTS.md, CLAUDE.md, Spaces, prompt library): qual seu nível?</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>L2-Q6: **D7 — Best Practices** (Champion, métricas DORA/DX, comunidade, compartilha prompts): qual seu nível?</t>
+          <t>L2-Q6: **DS-D7 Best Practices** (Champion, métricas DORA/DX, comunidade, compartilha prompts): qual seu nível?</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>L2-Q7: **D8 — Security &amp; Governance** (política IA, GHAS, SBOM, JIT permissions, red-lines de agents, audit): qual seu nível?</t>
+          <t>L2-Q7: **DS-D8 Security &amp; Governance** (política IA, GHAS, SBOM, JIT permissions, red-lines de agents, audit): qual seu nível?</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>D8 — Security &amp; Governance (GHAS, SBOM, red-lines); D5 — Agent Concepts (custom agents, MCP, A2A)</t>
+          <t>DS-D8 Security &amp; Governance (GHAS, SBOM, red-lines); DS-D5 Agent Concepts (custom agents, MCP, A2A)</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>D3 — MS/GitHub Tooling (Foundry, Spaces, Spec Kit, MCP); D6 — Instructions / Memory (instructions files, prompt library); D7 — Best Practices (DORA, comunidade, mentoria); D4 — AI Dev Practices (TDD com IA, SDD); D2 — Copilot Adoption (modos avançados, Coding Agent)</t>
+          <t>DS-D3 MS/GitHub Tooling (Foundry, Spaces, Spec Kit, MCP); DS-D6 Instructions / Memory (instructions files, prompt library); DS-D7 Best Practices (DORA, comunidade, mentoria); DS-D4 AI Dev Practices (TDD com IA, SDD); DS-D2 Copilot Adoption (modos avançados, Coding Agent)</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>D8 — Security &amp; Governance (GHAS, SBOM, red-lines); D5 — Agent Concepts (custom agents, MCP, A2A); D2 — Copilot Adoption (modos avançados, Coding Agent); D6 — Instructions / Memory (instructions files, prompt library); D7 — Best Practices (DORA, comunidade, mentoria)</t>
+          <t>DS-D8 Security &amp; Governance (GHAS, SBOM, red-lines); DS-D5 Agent Concepts (custom agents, MCP, A2A); DS-D2 Copilot Adoption (modos avançados, Coding Agent); DS-D6 Instructions / Memory (instructions files, prompt library); DS-D7 Best Practices (DORA, comunidade, mentoria)</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>D7 — Best Practices (DORA, comunidade, mentoria); D3 — MS/GitHub Tooling (Foundry, Spaces, Spec Kit, MCP); D2 — Copilot Adoption (modos avançados, Coding Agent); D6 — Instructions / Memory (instructions files, prompt library)</t>
+          <t>DS-D7 Best Practices (DORA, comunidade, mentoria); DS-D3 MS/GitHub Tooling (Foundry, Spaces, Spec Kit, MCP); DS-D2 Copilot Adoption (modos avançados, Coding Agent); DS-D6 Instructions / Memory (instructions files, prompt library)</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>D3 — MS/GitHub Tooling (Foundry, Spaces, Spec Kit, MCP); D6 — Instructions / Memory (instructions files, prompt library)</t>
+          <t>DS-D3 MS/GitHub Tooling (Foundry, Spaces, Spec Kit, MCP); DS-D6 Instructions / Memory (instructions files, prompt library)</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1614,9 +1614,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -1631,9 +1629,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr"/>
-    </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
@@ -1648,9 +1644,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
@@ -1693,9 +1687,7 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
-    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>

--- a/survey-learning/template-export-forms-learning.xlsx
+++ b/survey-learning/template-export-forms-learning.xlsx
@@ -566,7 +566,7 @@
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>L3-Q2: Por que escolheu essas 3 dimensões? (1-2 frases — opcional mas ajuda muito)</t>
+          <t>L3-Q2: Por que escolheu essas 3 dimensões? (1-2 frases: opcional mas ajuda muito)</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
@@ -711,37 +711,37 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>L3 — Uso Agent + Spaces, mensuro ganho</t>
+          <t>L3: Uso Agent + Spaces, mensuro ganho</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>L3 — Uso 4+ ferramentas avançadas</t>
+          <t>L3: Uso 4+ ferramentas avançadas</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>L3 — Trato IA como pair em várias fases</t>
+          <t>L3: Trato IA como pair em várias fases</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L3 — Já criei custom agents/skills/prompts</t>
+          <t>L3: Já criei custom agents/skills/prompts</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>L3 — Time mantém ativamente</t>
+          <t>L3: Time mantém ativamente</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>L3 — Mensuro DORA/DX + compartilho com colegas</t>
+          <t>L3: Mensuro DORA/DX + compartilho com colegas</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>L3 — Scanners obrigatórios + SBOM + treinamento</t>
+          <t>L3: Scanners obrigatórios + SBOM + treinamento</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -761,7 +761,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>A2A (Agent-to-Agent) protocol; Microsoft Foundry — visão geral; Azure OpenAI Service (API direta); Foundry Agent Service (criar agentes)</t>
+          <t>A2A (Agent-to-Agent) protocol; Microsoft Foundry, visão geral; Azure OpenAI Service (API direta); Foundry Agent Service (criar agentes)</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Sim — quero ser Champion ativo</t>
+          <t>Sim, quero ser Champion ativo</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -811,12 +811,12 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>Sim — mentor sênior em IA</t>
+          <t>Sim, mentor sênior em IA</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>Talvez — depende do tópico</t>
+          <t>Talvez, depende do tópico</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>Falta de orçamento para cursos pagos; Não sei por onde começar; Falta de treinamento estruturado; Tudo bem — sem barreiras significativas; Política de segurança bloqueia testes</t>
+          <t>Falta de orçamento para cursos pagos; Não sei por onde começar; Falta de treinamento estruturado; Tudo bem, sem barreiras significativas; Política de segurança bloqueia testes</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Sim — quero ver o plano e os workshops sugeridos</t>
+          <t>Sim, quero ver o plano e os workshops sugeridos</t>
         </is>
       </c>
     </row>
@@ -896,37 +896,37 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>L2 — Uso Ask/Edit no dia-a-dia</t>
+          <t>L2: Uso Ask/Edit no dia-a-dia</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>L2 — Uso 2-3 ferramentas básicas</t>
+          <t>L2: Uso 2-3 ferramentas básicas</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>L2 — TDD ou SDD ocasional</t>
+          <t>L2: TDD ou SDD ocasional</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L2 — Conheço modos do Copilot</t>
+          <t>L2: Conheço modos do Copilot</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>L2 — Uso e atualizo ocasionalmente</t>
+          <t>L2: Uso e atualizo ocasionalmente</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>L2 — Tenho Champion no time</t>
+          <t>L2: Tenho Champion no time</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>L2 — GHAS ativo + política básica</t>
+          <t>L2: GHAS ativo + política básica</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>A2A (Agent-to-Agent) protocol; Foundry Memory (long-term context); Microsoft Foundry — visão geral; Multi-agent orchestration; Não tenho interesse em Foundry hoje</t>
+          <t>A2A (Agent-to-Agent) protocol; Foundry Memory (long-term context); Microsoft Foundry, visão geral; Multi-agent orchestration; Não tenho interesse em Foundry hoje</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Sim — quero ser Champion ativo</t>
+          <t>Sim, quero ser Champion ativo</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>Não — prefiro auto-aprendizado</t>
+          <t>Não, prefiro auto-aprendizado</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Sim — quero ver o plano e os workshops sugeridos</t>
+          <t>Sim, quero ver o plano e os workshops sugeridos</t>
         </is>
       </c>
     </row>
@@ -1081,37 +1081,37 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>L3 — Uso Agent + Spaces, mensuro ganho</t>
+          <t>L3: Uso Agent + Spaces, mensuro ganho</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>L3 — Uso 4+ ferramentas avançadas</t>
+          <t>L3: Uso 4+ ferramentas avançadas</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>L3 — Trato IA como pair em várias fases</t>
+          <t>L3: Trato IA como pair em várias fases</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L3 — Já criei custom agents/skills/prompts</t>
+          <t>L3: Já criei custom agents/skills/prompts</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>L3 — Time mantém ativamente</t>
+          <t>L3: Time mantém ativamente</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>L3 — Mensuro DORA/DX + compartilho com colegas</t>
+          <t>L3: Mensuro DORA/DX + compartilho com colegas</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>L3 — Scanners obrigatórios + SBOM + treinamento</t>
+          <t>L3: Scanners obrigatórios + SBOM + treinamento</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>Coding Agent (autônomo no GitHub.com — assigna issue, abre PR); Modo Ask (perguntas eficazes); Copilot Spaces (contexto compartilhado); Test generation; Modo Agent (autônomo no IDE)</t>
+          <t>Coding Agent (autônomo no GitHub.com, assigna issue, abre PR); Modo Ask (perguntas eficazes); Copilot Spaces (contexto compartilhado); Test generation; Modo Agent (autônomo no IDE)</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>Multi-agent orchestration; Não tenho interesse em Foundry hoje; Microsoft Foundry — visão geral; Connectors (Dynamics, SAP, SharePoint)</t>
+          <t>Multi-agent orchestration; Não tenho interesse em Foundry hoje; Microsoft Foundry, visão geral; Connectors (Dynamics, SAP, SharePoint)</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>Sexta tarde (low-stress); Almoço (lunch &amp; learn); Manhã de quarta/quinta; Não consigo síncrono — só self-paced</t>
+          <t>Sexta tarde (low-stress); Almoço (lunch &amp; learn); Manhã de quarta/quinta; Não consigo síncrono, só self-paced</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>Talvez — depende do tópico</t>
+          <t>Talvez, depende do tópico</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>Tudo bem — sem barreiras significativas; Falta de licença para Foundry / Azure AI</t>
+          <t>Tudo bem, sem barreiras significativas; Falta de licença para Foundry / Azure AI</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
@@ -1266,37 +1266,37 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>L1 — Sei o básico (inline completion)</t>
+          <t>L1: Sei o básico (inline completion)</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>L1 — Conheço de nome</t>
+          <t>L1: Conheço de nome</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>L1 — Uso IA pontualmente</t>
+          <t>L1: Uso IA pontualmente</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L1 — Conheço só o básico</t>
+          <t>L1: Conheço só o básico</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>L1 — Tenho 1 arquivo básico</t>
+          <t>L1: Tenho 1 arquivo básico</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>L1 — Auto-aprendizado isolado</t>
+          <t>L1: Auto-aprendizado isolado</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>L1 — Política informal</t>
+          <t>L1: Política informal</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>A2A (Agent-to-Agent) protocol; Azure OpenAI Service (API direta); Não tenho interesse em Foundry hoje; MCP (Model Context Protocol) + Foundry MCP server; Microsoft Foundry — visão geral</t>
+          <t>A2A (Agent-to-Agent) protocol; Azure OpenAI Service (API direta); Não tenho interesse em Foundry hoje; MCP (Model Context Protocol) + Foundry MCP server; Microsoft Foundry, visão geral</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1366,12 +1366,12 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>Não — prefiro auto-aprendizado</t>
+          <t>Não, prefiro auto-aprendizado</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>Sim — em vários tópicos</t>
+          <t>Sim, em vários tópicos</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -1451,37 +1451,37 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>L2 — Uso Ask/Edit no dia-a-dia</t>
+          <t>L2: Uso Ask/Edit no dia-a-dia</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>L2 — Uso 2-3 ferramentas básicas</t>
+          <t>L2: Uso 2-3 ferramentas básicas</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>L2 — TDD ou SDD ocasional</t>
+          <t>L2: TDD ou SDD ocasional</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L2 — Conheço modos do Copilot</t>
+          <t>L2: Conheço modos do Copilot</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>L2 — Uso e atualizo ocasionalmente</t>
+          <t>L2: Uso e atualizo ocasionalmente</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>L2 — Tenho Champion no time</t>
+          <t>L2: Tenho Champion no time</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>L2 — GHAS ativo + política básica</t>
+          <t>L2: GHAS ativo + política básica</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>Modo Ask (perguntas eficazes); Coding Agent (autônomo no GitHub.com — assigna issue, abre PR); Copilot Spaces (contexto compartilhado)</t>
+          <t>Modo Ask (perguntas eficazes); Coding Agent (autônomo no GitHub.com, assigna issue, abre PR); Copilot Spaces (contexto compartilhado)</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>Após expediente (com hora extra); Não consigo síncrono — só self-paced</t>
+          <t>Após expediente (com hora extra); Não consigo síncrono, só self-paced</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Sim — quero ser Champion ativo</t>
+          <t>Sim, quero ser Champion ativo</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>Não — prefiro auto-aprendizado</t>
+          <t>Não, prefiro auto-aprendizado</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>Sim — em vários tópicos</t>
+          <t>Sim, em vários tópicos</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
